--- a/data/trans_bre/P37-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P37-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,35</t>
+          <t>-4,13; 3,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 3,16</t>
+          <t>-5,77; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,94</t>
+          <t>-3,63; 4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,96</t>
+          <t>1,66; 10,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 25,28</t>
+          <t>-24,8; 23,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 16,78</t>
+          <t>-25,18; 17,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 32,96</t>
+          <t>-18,92; 29,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 38,63</t>
+          <t>4,61; 36,23</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,57</t>
+          <t>-1,02; 5,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,94</t>
+          <t>-2,86; 4,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,09</t>
+          <t>-0,11; 6,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 25,59</t>
+          <t>7,6; 25,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 44,72</t>
+          <t>-7,23; 46,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 31,03</t>
+          <t>-14,14; 28,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 55,67</t>
+          <t>-1,52; 51,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,42; 211,55</t>
+          <t>27,14; 201,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,95</t>
+          <t>-1,0; 6,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,46</t>
+          <t>-2,4; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,23</t>
+          <t>-4,91; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 41,43</t>
+          <t>0,17; 43,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 65,79</t>
+          <t>-6,78; 59,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 39,2</t>
+          <t>-13,98; 41,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 21,44</t>
+          <t>-26,34; 20,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 148,73</t>
+          <t>0,52; 147,92</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,57</t>
+          <t>-0,6; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,34</t>
+          <t>-2,49; 4,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,79</t>
+          <t>-1,42; 5,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 4,81</t>
+          <t>-7,08; 5,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 47,12</t>
+          <t>-4,16; 46,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 28,79</t>
+          <t>-13,17; 29,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 41,55</t>
+          <t>-8,45; 38,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 13,84</t>
+          <t>-18,81; 14,97</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,78</t>
+          <t>0,24; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,44</t>
+          <t>-1,31; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,46</t>
+          <t>-0,15; 3,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 22,68</t>
+          <t>4,43; 20,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 29,0</t>
+          <t>1,86; 29,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 14,79</t>
+          <t>-6,84; 15,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 23,56</t>
+          <t>-1,06; 23,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 91,46</t>
+          <t>14,03; 79,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P37-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P37-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,24</t>
+          <t>-3,91; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 3,02</t>
+          <t>-5,42; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,52</t>
+          <t>-3,25; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,5</t>
+          <t>0,44; 9,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 23,42</t>
+          <t>-23,49; 29,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 17,1</t>
+          <t>-23,19; 20,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 29,94</t>
+          <t>-17,33; 34,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 36,23</t>
+          <t>1,24; 32,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,28</t>
+          <t>8,93</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,77</t>
+          <t>-1,41; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,26</t>
+          <t>-2,38; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,81</t>
+          <t>0,22; 6,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 25,13</t>
+          <t>5,18; 12,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 46,21</t>
+          <t>-9,7; 44,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 28,13</t>
+          <t>-12,43; 26,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 51,2</t>
+          <t>1,27; 52,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 201,97</t>
+          <t>17,79; 52,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,64</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,84</t>
+          <t>-0,71; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,56</t>
+          <t>-2,7; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,0</t>
+          <t>-4,69; 2,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 43,42</t>
+          <t>-2,43; 6,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 59,58</t>
+          <t>-5,37; 64,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 41,26</t>
+          <t>-15,78; 39,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 20,46</t>
+          <t>-25,05; 19,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 147,92</t>
+          <t>-7,51; 23,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,53</t>
+          <t>-0,63; 5,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,45</t>
+          <t>-2,36; 4,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 5,3</t>
+          <t>-1,29; 5,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 5,31</t>
+          <t>-1,06; 6,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 46,69</t>
+          <t>-4,38; 48,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 29,56</t>
+          <t>-12,78; 31,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 38,04</t>
+          <t>-7,55; 38,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 14,97</t>
+          <t>-2,72; 20,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,72</t>
+          <t>0,26; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,48</t>
+          <t>-1,34; 2,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,48</t>
+          <t>-0,33; 3,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 20,9</t>
+          <t>2,8; 7,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 29,17</t>
+          <t>1,67; 28,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 15,07</t>
+          <t>-7,15; 15,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 23,6</t>
+          <t>-1,99; 23,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 79,88</t>
+          <t>8,78; 24,14</t>
         </is>
       </c>
     </row>
